--- a/Problem_1_yield_curve_predict.xlsx
+++ b/Problem_1_yield_curve_predict.xlsx
@@ -476,31 +476,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.88970499680111</v>
+        <v>27.58099625797802</v>
       </c>
       <c r="C2" t="n">
-        <v>27.24872381422451</v>
+        <v>27.94806821387961</v>
       </c>
       <c r="D2" t="n">
-        <v>27.65995375796551</v>
+        <v>28.36905696116706</v>
       </c>
       <c r="E2" t="n">
-        <v>28.59763525130065</v>
+        <v>29.33095343106748</v>
       </c>
       <c r="F2" t="n">
-        <v>30.26621065186217</v>
+        <v>31.0481161894927</v>
       </c>
       <c r="G2" t="n">
-        <v>31.88775602369663</v>
+        <v>32.72129838356144</v>
       </c>
       <c r="H2" t="n">
-        <v>36.73854494252559</v>
+        <v>37.73183067972967</v>
       </c>
       <c r="I2" t="n">
-        <v>46.85722438706912</v>
+        <v>48.14225205623424</v>
       </c>
       <c r="J2" t="n">
-        <v>66.04634858124935</v>
+        <v>67.75484513204388</v>
       </c>
     </row>
     <row r="3">
@@ -510,31 +510,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.46988237146578</v>
+        <v>27.32921963153298</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81515750736964</v>
+        <v>27.68686749438694</v>
       </c>
       <c r="D3" t="n">
-        <v>27.2119310391754</v>
+        <v>28.09743409908447</v>
       </c>
       <c r="E3" t="n">
-        <v>28.1214539790146</v>
+        <v>29.03682404548405</v>
       </c>
       <c r="F3" t="n">
-        <v>29.75389310740491</v>
+        <v>30.71676784041536</v>
       </c>
       <c r="G3" t="n">
-        <v>31.35249258161637</v>
+        <v>32.35479035005949</v>
       </c>
       <c r="H3" t="n">
-        <v>36.15902495835235</v>
+        <v>37.24810898881027</v>
       </c>
       <c r="I3" t="n">
-        <v>46.12929585339079</v>
+        <v>47.32641909540914</v>
       </c>
       <c r="J3" t="n">
-        <v>64.79218858348193</v>
+        <v>66.12813076705383</v>
       </c>
     </row>
     <row r="4">
@@ -544,31 +544,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.08001190049905</v>
+        <v>27.01416174338617</v>
       </c>
       <c r="C4" t="n">
-        <v>26.41805273812856</v>
+        <v>27.36926335891812</v>
       </c>
       <c r="D4" t="n">
-        <v>26.80689511552265</v>
+        <v>27.77668392010152</v>
       </c>
       <c r="E4" t="n">
-        <v>27.69964721501777</v>
+        <v>28.70809507505579</v>
       </c>
       <c r="F4" t="n">
-        <v>29.30597962473399</v>
+        <v>30.3718226797033</v>
       </c>
       <c r="G4" t="n">
-        <v>30.88231676840072</v>
+        <v>31.99289677408134</v>
       </c>
       <c r="H4" t="n">
-        <v>35.6270629358296</v>
+        <v>36.83862651630238</v>
       </c>
       <c r="I4" t="n">
-        <v>45.44576310086944</v>
+        <v>46.8555646146865</v>
       </c>
       <c r="J4" t="n">
-        <v>63.74249777224254</v>
+        <v>65.62762875068314</v>
       </c>
     </row>
     <row r="5">
@@ -578,31 +578,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.74602977574192</v>
+        <v>26.80852217606993</v>
       </c>
       <c r="C5" t="n">
-        <v>26.07921221054164</v>
+        <v>27.16083995265096</v>
       </c>
       <c r="D5" t="n">
-        <v>26.46250074904514</v>
+        <v>27.56512560395796</v>
       </c>
       <c r="E5" t="n">
-        <v>27.34261320362977</v>
+        <v>28.48959565915678</v>
       </c>
       <c r="F5" t="n">
-        <v>28.92641667581983</v>
+        <v>30.14161204648744</v>
       </c>
       <c r="G5" t="n">
-        <v>30.48063866584108</v>
+        <v>31.75192991815763</v>
       </c>
       <c r="H5" t="n">
-        <v>35.15696092193332</v>
+        <v>36.56738271604712</v>
       </c>
       <c r="I5" t="n">
-        <v>44.82318636759319</v>
+        <v>46.52210677488224</v>
       </c>
       <c r="J5" t="n">
-        <v>62.81435894285422</v>
+        <v>65.17102870029457</v>
       </c>
     </row>
     <row r="6">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.45902253442535</v>
+        <v>26.66497521509561</v>
       </c>
       <c r="C6" t="n">
-        <v>25.78777983953252</v>
+        <v>27.01263774205017</v>
       </c>
       <c r="D6" t="n">
-        <v>26.1659294468872</v>
+        <v>27.41183822605132</v>
       </c>
       <c r="E6" t="n">
-        <v>27.03405251448417</v>
+        <v>28.32563254629034</v>
       </c>
       <c r="F6" t="n">
-        <v>28.59567492848003</v>
+        <v>29.96130184412578</v>
       </c>
       <c r="G6" t="n">
-        <v>30.12750442751083</v>
+        <v>31.55800111079589</v>
       </c>
       <c r="H6" t="n">
-        <v>34.73420551052998</v>
+        <v>36.33686115813045</v>
       </c>
       <c r="I6" t="n">
-        <v>44.25340017251605</v>
+        <v>46.20246414786348</v>
       </c>
       <c r="J6" t="n">
-        <v>61.97160494006289</v>
+        <v>64.63223723554601</v>
       </c>
     </row>
     <row r="7">
@@ -646,31 +646,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.20821545041197</v>
+        <v>26.50902117534262</v>
       </c>
       <c r="C7" t="n">
-        <v>25.53253839146037</v>
+        <v>26.85271830939206</v>
       </c>
       <c r="D7" t="n">
-        <v>25.90552949260298</v>
+        <v>27.24741847151594</v>
       </c>
       <c r="E7" t="n">
-        <v>26.76159456044745</v>
+        <v>28.15110918486492</v>
       </c>
       <c r="F7" t="n">
-        <v>28.30090371187527</v>
+        <v>29.76927108265739</v>
       </c>
       <c r="G7" t="n">
-        <v>29.8103083814338</v>
+        <v>31.34938901254177</v>
       </c>
       <c r="H7" t="n">
-        <v>34.34849755272147</v>
+        <v>36.07972272988858</v>
       </c>
       <c r="I7" t="n">
-        <v>43.72851155368161</v>
+        <v>45.84334244848147</v>
       </c>
       <c r="J7" t="n">
-        <v>61.19828911901239</v>
+        <v>64.0734079881524</v>
       </c>
     </row>
   </sheetData>
@@ -746,31 +746,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.33414530675169</v>
+        <v>27.58099625797802</v>
       </c>
       <c r="C2" t="n">
-        <v>28.52755639512268</v>
+        <v>27.94806821387961</v>
       </c>
       <c r="D2" t="n">
-        <v>28.76472342344909</v>
+        <v>28.36905696116706</v>
       </c>
       <c r="E2" t="n">
-        <v>29.36657023379358</v>
+        <v>29.33095343106748</v>
       </c>
       <c r="F2" t="n">
-        <v>30.63158013591725</v>
+        <v>31.0481161894927</v>
       </c>
       <c r="G2" t="n">
-        <v>32.05894706187505</v>
+        <v>32.72129838356144</v>
       </c>
       <c r="H2" t="n">
-        <v>37.00200090464109</v>
+        <v>37.73183067972967</v>
       </c>
       <c r="I2" t="n">
-        <v>47.96913073985129</v>
+        <v>48.14225205623424</v>
       </c>
       <c r="J2" t="n">
-        <v>67.21261871186979</v>
+        <v>67.75484513204388</v>
       </c>
     </row>
     <row r="3">
@@ -780,31 +780,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.39517582889389</v>
+        <v>27.32921963153298</v>
       </c>
       <c r="C3" t="n">
-        <v>28.58811657837427</v>
+        <v>27.68686749438694</v>
       </c>
       <c r="D3" t="n">
-        <v>28.82474342965795</v>
+        <v>28.09743409908447</v>
       </c>
       <c r="E3" t="n">
-        <v>29.42535857497666</v>
+        <v>29.03682404548405</v>
       </c>
       <c r="F3" t="n">
-        <v>30.68821066318148</v>
+        <v>30.71676784041536</v>
       </c>
       <c r="G3" t="n">
-        <v>32.11357031325775</v>
+        <v>32.35479035005949</v>
       </c>
       <c r="H3" t="n">
-        <v>37.05139235885152</v>
+        <v>37.24810898881027</v>
       </c>
       <c r="I3" t="n">
-        <v>48.0108042020539</v>
+        <v>47.32641909540914</v>
       </c>
       <c r="J3" t="n">
-        <v>67.24543604270825</v>
+        <v>66.12813076705383</v>
       </c>
     </row>
     <row r="4">
@@ -814,31 +814,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.35451559352774</v>
+        <v>27.01416174338617</v>
       </c>
       <c r="C4" t="n">
-        <v>28.55088764139149</v>
+        <v>27.36926335891812</v>
       </c>
       <c r="D4" t="n">
-        <v>28.79138893594464</v>
+        <v>27.77668392010152</v>
       </c>
       <c r="E4" t="n">
-        <v>29.400568747649</v>
+        <v>28.70809507505579</v>
       </c>
       <c r="F4" t="n">
-        <v>30.67749642007259</v>
+        <v>30.3718226797033</v>
       </c>
       <c r="G4" t="n">
-        <v>32.11484389757573</v>
+        <v>31.99289677408134</v>
       </c>
       <c r="H4" t="n">
-        <v>37.07851600772858</v>
+        <v>36.83862651630238</v>
       </c>
       <c r="I4" t="n">
-        <v>48.05984614460115</v>
+        <v>46.8555646146865</v>
       </c>
       <c r="J4" t="n">
-        <v>67.29024602084128</v>
+        <v>65.62762875068314</v>
       </c>
     </row>
     <row r="5">
@@ -848,31 +848,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.39872953486431</v>
+        <v>26.80852217606993</v>
       </c>
       <c r="C5" t="n">
-        <v>28.59444005953866</v>
+        <v>27.16083995265096</v>
       </c>
       <c r="D5" t="n">
-        <v>28.83419417872279</v>
+        <v>27.56512560395796</v>
       </c>
       <c r="E5" t="n">
-        <v>29.44172141877255</v>
+        <v>28.48959565915678</v>
       </c>
       <c r="F5" t="n">
-        <v>30.71592997429487</v>
+        <v>30.14161204648744</v>
       </c>
       <c r="G5" t="n">
-        <v>32.15095758627992</v>
+        <v>31.75192991815763</v>
       </c>
       <c r="H5" t="n">
-        <v>37.10960559198324</v>
+        <v>36.56738271604712</v>
       </c>
       <c r="I5" t="n">
-        <v>48.08659716733654</v>
+        <v>46.52210677488224</v>
       </c>
       <c r="J5" t="n">
-        <v>67.31758688417659</v>
+        <v>65.17102870029457</v>
       </c>
     </row>
     <row r="6">
@@ -882,31 +882,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.36682439911986</v>
+        <v>26.66497521509561</v>
       </c>
       <c r="C6" t="n">
-        <v>28.56237171285729</v>
+        <v>27.01263774205017</v>
       </c>
       <c r="D6" t="n">
-        <v>28.80194127292425</v>
+        <v>27.41183822605132</v>
       </c>
       <c r="E6" t="n">
-        <v>29.40905942027227</v>
+        <v>28.32563254629034</v>
       </c>
       <c r="F6" t="n">
-        <v>30.68259168835158</v>
+        <v>29.96130184412578</v>
       </c>
       <c r="G6" t="n">
-        <v>32.11703829358551</v>
+        <v>31.55800111079589</v>
       </c>
       <c r="H6" t="n">
-        <v>37.07440663737896</v>
+        <v>36.33686115813045</v>
       </c>
       <c r="I6" t="n">
-        <v>48.05021581456615</v>
+        <v>46.20246414786348</v>
       </c>
       <c r="J6" t="n">
-        <v>67.2811268642981</v>
+        <v>64.63223723554601</v>
       </c>
     </row>
     <row r="7">
@@ -916,31 +916,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.39172374335676</v>
+        <v>26.50902117534262</v>
       </c>
       <c r="C7" t="n">
-        <v>28.58744376672002</v>
+        <v>26.85271830939206</v>
       </c>
       <c r="D7" t="n">
-        <v>28.82720807473447</v>
+        <v>27.24741847151594</v>
       </c>
       <c r="E7" t="n">
-        <v>29.43475562086867</v>
+        <v>28.15110918486492</v>
       </c>
       <c r="F7" t="n">
-        <v>30.70898966389654</v>
+        <v>29.76927108265739</v>
       </c>
       <c r="G7" t="n">
-        <v>32.14402898141299</v>
+        <v>31.34938901254177</v>
       </c>
       <c r="H7" t="n">
-        <v>37.10264892891387</v>
+        <v>36.07972272988858</v>
       </c>
       <c r="I7" t="n">
-        <v>48.0794230803507</v>
+        <v>45.84334244848147</v>
       </c>
       <c r="J7" t="n">
-        <v>67.30984434936867</v>
+        <v>64.0734079881524</v>
       </c>
     </row>
   </sheetData>
